--- a/KURIKULUM2026_REVISI/BUKU_KURIKULUM_OBE_SISTEKIN_2026_FINAL.xlsx
+++ b/KURIKULUM2026_REVISI/BUKU_KURIKULUM_OBE_SISTEKIN_2026_FINAL.xlsx
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>STI-627, MKU-204</t>
+          <t>STI-727, MKU-204</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-624` Integrasi AI</t>
+          <t>`STI-413`, `STI-726` Integrasi AI</t>
         </is>
       </c>
       <c r="H231" s="8" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
-          <t>`STI-626`, `STI-521` IoT</t>
+          <t>`STI-726`, `STI-521` IoT</t>
         </is>
       </c>
       <c r="H233" s="8" t="inlineStr">
@@ -6519,7 +6519,7 @@
       <c r="B256" s="10" t="inlineStr"/>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>• STI-626 Deep Learning (3)</t>
+          <t>• STI-726 Deep Learning (3)</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr"/>
@@ -6529,7 +6529,7 @@
       <c r="B257" s="9" t="inlineStr"/>
       <c r="C257" s="7" t="inlineStr">
         <is>
-          <t>• STI-627 Platform Eng (3)</t>
+          <t>• STI-727 Platform Eng (3)</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       <c r="B266" s="10" t="inlineStr"/>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>• STI-624 Integrasi AI (3)</t>
+          <t>• STI-726 Integrasi AI (3)</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr"/>
@@ -6649,7 +6649,7 @@
       <c r="B267" s="9" t="inlineStr"/>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>• STI-625 Smart City (2)</t>
+          <t>• STI-727 Smart City (2)</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr"/>
@@ -9894,7 +9894,7 @@
     <row r="453" ht="16" customHeight="1">
       <c r="A453" s="7" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="B453" s="7" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D453" s="7" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="E453" s="7" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="B514" s="8" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C514" s="8" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B515" s="7" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C515" s="7" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="B516" s="8" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C516" s="8" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B517" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C517" s="7" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="D582" s="8" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-627`</t>
+          <t>`STI-306`, `STI-727`</t>
         </is>
       </c>
       <c r="E582" s="8" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C584" s="8" t="inlineStr">
         <is>
-          <t>`STI-418`, `STI-626`, `STB-501`, `STB-602`</t>
+          <t>`STI-418`, `STI-726`, `STB-501`, `STB-602`</t>
         </is>
       </c>
       <c r="D584" s="8" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="D587" s="7" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-625`</t>
+          <t>`STI-306`, `STI-727`</t>
         </is>
       </c>
       <c r="E587" s="7" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="C590" s="8" t="inlineStr">
         <is>
-          <t>`STI-311`, `STI-416`, `STI-522`, `STI-627`</t>
+          <t>`STI-311`, `STI-416`, `STI-522`, `STI-727`</t>
         </is>
       </c>
       <c r="D590" s="8" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="C594" s="8" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-414`, `STI-624`, `STA-602`, `STA-702`</t>
+          <t>`STI-307`, `STI-414`, `STI-726`, `STA-602`, `STA-702`</t>
         </is>
       </c>
       <c r="D594" s="8" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="D597" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`, `STC-702`</t>
+          <t>`STI-727`, `STC-702`</t>
         </is>
       </c>
       <c r="E597" s="7" t="inlineStr">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="D598" s="8" t="inlineStr">
         <is>
-          <t>`STI-418`, `STI-625`, `STB-701`</t>
+          <t>`STI-418`, `STI-727`, `STB-701`</t>
         </is>
       </c>
       <c r="E598" s="8" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="C604" s="8" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-413`, `STI-414`, `STI-519`, `STI-624`</t>
+          <t>`STI-307`, `STI-413`, `STI-414`, `STI-519`, `STI-726`</t>
         </is>
       </c>
       <c r="D604" s="8" t="inlineStr">
@@ -16270,7 +16270,7 @@
       </c>
       <c r="C606" s="8" t="inlineStr">
         <is>
-          <t>`STI-311`, `STI-416`, `STI-522`, `STI-627`</t>
+          <t>`STI-311`, `STI-416`, `STI-522`, `STI-727`</t>
         </is>
       </c>
       <c r="D606" s="8" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="C608" s="8" t="inlineStr">
         <is>
-          <t>`STI-418`, `STI-626`, `STB-501`</t>
+          <t>`STI-418`, `STI-726`, `STB-501`</t>
         </is>
       </c>
       <c r="D608" s="8" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C609" s="7" t="inlineStr">
         <is>
-          <t>`STI-624`, `STI-627`, `FST-610`</t>
+          <t>`STI-726`, `STI-727`, `FST-610`</t>
         </is>
       </c>
       <c r="D609" s="7" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="C613" s="7" t="inlineStr">
         <is>
-          <t>`STI-309`, `STI-416`, `STI-627`</t>
+          <t>`STI-309`, `STI-416`, `STI-727`</t>
         </is>
       </c>
       <c r="D613" s="7" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B659" s="7" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C659" s="7" t="inlineStr">
@@ -18545,7 +18545,7 @@
       </c>
       <c r="B660" s="8" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C660" s="8" t="inlineStr">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="B661" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C661" s="7" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="B662" s="8" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C662" s="8" t="inlineStr">
@@ -45131,7 +45131,7 @@
       </c>
       <c r="B2002" s="7" t="inlineStr">
         <is>
-          <t>**STI-624 — Integrasi Layanan Cerdas Berbasis AI** (*AI-Based Smart Services Integration*)</t>
+          <t>**STI-726 — Integrasi Layanan Cerdas Berbasis AI** (*AI-Based Smart Services Integration*)</t>
         </is>
       </c>
     </row>
@@ -45835,7 +45835,7 @@
       </c>
       <c r="B2038" s="7" t="inlineStr">
         <is>
-          <t>**STI-625 — Smart City &amp; Pemerintahan Digital** (*Smart City &amp; Digital Governance*)</t>
+          <t>**STI-727 — Smart City &amp; Pemerintahan Digital** (*Smart City &amp; Digital Governance*)</t>
         </is>
       </c>
     </row>
@@ -46539,7 +46539,7 @@
       </c>
       <c r="B2074" s="7" t="inlineStr">
         <is>
-          <t>**STI-626 — Deep Learning &amp; Neural Networks** (*Deep Learning &amp; Neural Networks*)</t>
+          <t>**STI-726 — Deep Learning &amp; Neural Networks** (*Deep Learning &amp; Neural Networks*)</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="B2110" s="7" t="inlineStr">
         <is>
-          <t>**STI-627 — Digital Platform Engineering** (*Digital Platform Engineering*)</t>
+          <t>**STI-727 — Digital Platform Engineering** (*Digital Platform Engineering*)</t>
         </is>
       </c>
     </row>
@@ -54231,7 +54231,7 @@
       </c>
       <c r="B2469" s="8" t="inlineStr">
         <is>
-          <t>`STI-413` Machine Learning &amp; `STI-624` Integrasi AI</t>
+          <t>`STI-413` Machine Learning &amp; `STI-726` Integrasi AI</t>
         </is>
       </c>
     </row>
@@ -55617,7 +55617,7 @@
       </c>
       <c r="B2540" s="8" t="inlineStr">
         <is>
-          <t>`STI-626` Deep Learning &amp; `STI-521` IoT</t>
+          <t>`STI-726` Deep Learning &amp; `STI-521` IoT</t>
         </is>
       </c>
     </row>
